--- a/src/assets/Clasificación de Clientes.xlsx
+++ b/src/assets/Clasificación de Clientes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,20 +425,47 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="str">
-        <v>Golden</v>
+        <v>Standardeds</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Golden</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>asadasd</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>bcd</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="str">
+        <v>prueba</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
 </file>